--- a/r4-core-157-add-vbpk-as-patientidentifier/all-profiles.xlsx
+++ b/r4-core-157-add-vbpk-as-patientidentifier/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T08:37:32+00:00</t>
+    <t>2026-04-30T08:59:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
